--- a/data/nzd0494/nzd0494.xlsx
+++ b/data/nzd0494/nzd0494.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M646"/>
+  <dimension ref="A1:M652"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29518,6 +29518,276 @@
         <v>357.69</v>
       </c>
       <c r="M646" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:13:56+00:00</t>
+        </is>
+      </c>
+      <c r="B647" t="n">
+        <v>332.99</v>
+      </c>
+      <c r="C647" t="n">
+        <v>344.75</v>
+      </c>
+      <c r="D647" t="n">
+        <v>350.51</v>
+      </c>
+      <c r="E647" t="n">
+        <v>350.2</v>
+      </c>
+      <c r="F647" t="n">
+        <v>350.03</v>
+      </c>
+      <c r="G647" t="n">
+        <v>346.65</v>
+      </c>
+      <c r="H647" t="n">
+        <v>354.65</v>
+      </c>
+      <c r="I647" t="n">
+        <v>366.67</v>
+      </c>
+      <c r="J647" t="n">
+        <v>372.06</v>
+      </c>
+      <c r="K647" t="n">
+        <v>362.27</v>
+      </c>
+      <c r="L647" t="n">
+        <v>360.82</v>
+      </c>
+      <c r="M647" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:19:55+00:00</t>
+        </is>
+      </c>
+      <c r="B648" t="n">
+        <v>333</v>
+      </c>
+      <c r="C648" t="n">
+        <v>344.06</v>
+      </c>
+      <c r="D648" t="n">
+        <v>348.65</v>
+      </c>
+      <c r="E648" t="n">
+        <v>350</v>
+      </c>
+      <c r="F648" t="n">
+        <v>349.65</v>
+      </c>
+      <c r="G648" t="n">
+        <v>346.98</v>
+      </c>
+      <c r="H648" t="n">
+        <v>355.28</v>
+      </c>
+      <c r="I648" t="n">
+        <v>367.84</v>
+      </c>
+      <c r="J648" t="n">
+        <v>373.45</v>
+      </c>
+      <c r="K648" t="n">
+        <v>363.39</v>
+      </c>
+      <c r="L648" t="n">
+        <v>362.99</v>
+      </c>
+      <c r="M648" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B649" t="n">
+        <v>332.93</v>
+      </c>
+      <c r="C649" t="n">
+        <v>344.56</v>
+      </c>
+      <c r="D649" t="n">
+        <v>348.67</v>
+      </c>
+      <c r="E649" t="n">
+        <v>350.53</v>
+      </c>
+      <c r="F649" t="n">
+        <v>350.04</v>
+      </c>
+      <c r="G649" t="n">
+        <v>347.94</v>
+      </c>
+      <c r="H649" t="n">
+        <v>355.28</v>
+      </c>
+      <c r="I649" t="n">
+        <v>367.55</v>
+      </c>
+      <c r="J649" t="n">
+        <v>373.87</v>
+      </c>
+      <c r="K649" t="n">
+        <v>364.48</v>
+      </c>
+      <c r="L649" t="n">
+        <v>363.63</v>
+      </c>
+      <c r="M649" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:15+00:00</t>
+        </is>
+      </c>
+      <c r="B650" t="n">
+        <v>332.04</v>
+      </c>
+      <c r="C650" t="n">
+        <v>344.44</v>
+      </c>
+      <c r="D650" t="n">
+        <v>348.74</v>
+      </c>
+      <c r="E650" t="n">
+        <v>349.96</v>
+      </c>
+      <c r="F650" t="n">
+        <v>350.3</v>
+      </c>
+      <c r="G650" t="n">
+        <v>347.79</v>
+      </c>
+      <c r="H650" t="n">
+        <v>355.41</v>
+      </c>
+      <c r="I650" t="n">
+        <v>366.64</v>
+      </c>
+      <c r="J650" t="n">
+        <v>373.15</v>
+      </c>
+      <c r="K650" t="n">
+        <v>363.99</v>
+      </c>
+      <c r="L650" t="n">
+        <v>362.48</v>
+      </c>
+      <c r="M650" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:14:16+00:00</t>
+        </is>
+      </c>
+      <c r="B651" t="n">
+        <v>331.45</v>
+      </c>
+      <c r="C651" t="n">
+        <v>344.04</v>
+      </c>
+      <c r="D651" t="n">
+        <v>348.6</v>
+      </c>
+      <c r="E651" t="n">
+        <v>349.54</v>
+      </c>
+      <c r="F651" t="n">
+        <v>349.94</v>
+      </c>
+      <c r="G651" t="n">
+        <v>347.64</v>
+      </c>
+      <c r="H651" t="n">
+        <v>355.02</v>
+      </c>
+      <c r="I651" t="n">
+        <v>366.11</v>
+      </c>
+      <c r="J651" t="n">
+        <v>371.97</v>
+      </c>
+      <c r="K651" t="n">
+        <v>364.21</v>
+      </c>
+      <c r="L651" t="n">
+        <v>362.06</v>
+      </c>
+      <c r="M651" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:32+00:00</t>
+        </is>
+      </c>
+      <c r="B652" t="n">
+        <v>331.45</v>
+      </c>
+      <c r="C652" t="n">
+        <v>344.51</v>
+      </c>
+      <c r="D652" t="n">
+        <v>349.08</v>
+      </c>
+      <c r="E652" t="n">
+        <v>349.73</v>
+      </c>
+      <c r="F652" t="n">
+        <v>350.32</v>
+      </c>
+      <c r="G652" t="n">
+        <v>348.16</v>
+      </c>
+      <c r="H652" t="n">
+        <v>355.52</v>
+      </c>
+      <c r="I652" t="n">
+        <v>366.12</v>
+      </c>
+      <c r="J652" t="n">
+        <v>372.38</v>
+      </c>
+      <c r="K652" t="n">
+        <v>364.56</v>
+      </c>
+      <c r="L652" t="n">
+        <v>362.08</v>
+      </c>
+      <c r="M652" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29534,7 +29804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B681"/>
+  <dimension ref="A1:B687"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36347,6 +36617,66 @@
       </c>
       <c r="B681" t="n">
         <v>-0.72</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B682" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B683" t="n">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B684" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B685" t="n">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B686" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B687" t="n">
+        <v>-0.06</v>
       </c>
     </row>
   </sheetData>
@@ -36515,28 +36845,28 @@
         <v>0.122</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.253783178019742</v>
+        <v>-0.2508906731333573</v>
       </c>
       <c r="J2" t="n">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="K2" t="n">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08465660057427937</v>
+        <v>0.08439075145266406</v>
       </c>
       <c r="M2" t="n">
-        <v>4.751635844148614</v>
+        <v>4.723802986192278</v>
       </c>
       <c r="N2" t="n">
-        <v>36.07899755157349</v>
+        <v>35.77233398198674</v>
       </c>
       <c r="O2" t="n">
-        <v>6.006579521788877</v>
+        <v>5.980997741346066</v>
       </c>
       <c r="P2" t="n">
-        <v>337.5840480813074</v>
+        <v>337.5512854333911</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -36597,28 +36927,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2475302908363653</v>
+        <v>-0.2434874674974391</v>
       </c>
       <c r="J3" t="n">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="K3" t="n">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1291750952890071</v>
+        <v>0.1275275728456753</v>
       </c>
       <c r="M3" t="n">
-        <v>3.732443010903525</v>
+        <v>3.717543746480941</v>
       </c>
       <c r="N3" t="n">
-        <v>21.40002716750137</v>
+        <v>21.24534405301581</v>
       </c>
       <c r="O3" t="n">
-        <v>4.626016338870991</v>
+        <v>4.609267192625722</v>
       </c>
       <c r="P3" t="n">
-        <v>348.8831572650447</v>
+        <v>348.8373493137251</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36675,28 +37005,28 @@
         <v>0.1492</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2022211784151623</v>
+        <v>-0.199468572137625</v>
       </c>
       <c r="J4" t="n">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="K4" t="n">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08503384250106061</v>
+        <v>0.08439466357780656</v>
       </c>
       <c r="M4" t="n">
-        <v>3.736292974167972</v>
+        <v>3.714566675924674</v>
       </c>
       <c r="N4" t="n">
-        <v>22.79670452544322</v>
+        <v>22.61024213449626</v>
       </c>
       <c r="O4" t="n">
-        <v>4.774589461455636</v>
+        <v>4.755022832174022</v>
       </c>
       <c r="P4" t="n">
-        <v>353.0032945307493</v>
+        <v>352.9721151298219</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36753,28 +37083,28 @@
         <v>0.1198</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1683804829440036</v>
+        <v>-0.162759351123446</v>
       </c>
       <c r="J5" t="n">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="K5" t="n">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06512727071507696</v>
+        <v>0.06205456632083406</v>
       </c>
       <c r="M5" t="n">
-        <v>3.634728388116875</v>
+        <v>3.626256418547872</v>
       </c>
       <c r="N5" t="n">
-        <v>21.08524659560005</v>
+        <v>20.97290814445818</v>
       </c>
       <c r="O5" t="n">
-        <v>4.591867440987387</v>
+        <v>4.579618777197309</v>
       </c>
       <c r="P5" t="n">
-        <v>351.5100521942627</v>
+        <v>351.4463620158937</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36831,28 +37161,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.06807377177054784</v>
+        <v>-0.06150718367852276</v>
       </c>
       <c r="J6" t="n">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="K6" t="n">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00849357845406673</v>
+        <v>0.007057587062186843</v>
       </c>
       <c r="M6" t="n">
-        <v>4.054522056528643</v>
+        <v>4.048803100759519</v>
       </c>
       <c r="N6" t="n">
-        <v>28.02657496342492</v>
+        <v>27.87933610494569</v>
       </c>
       <c r="O6" t="n">
-        <v>5.294013124598854</v>
+        <v>5.280088645557543</v>
       </c>
       <c r="P6" t="n">
-        <v>348.3612292289797</v>
+        <v>348.2868192795383</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36909,28 +37239,28 @@
         <v>0.1734</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.001896568853871393</v>
+        <v>-0.0004925276428860764</v>
       </c>
       <c r="J7" t="n">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="K7" t="n">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="L7" t="n">
-        <v>4.91044062245205e-06</v>
+        <v>3.378598177894432e-07</v>
       </c>
       <c r="M7" t="n">
-        <v>4.832868886421623</v>
+        <v>4.795404112844887</v>
       </c>
       <c r="N7" t="n">
-        <v>37.95073592074561</v>
+        <v>37.60862507778143</v>
       </c>
       <c r="O7" t="n">
-        <v>6.160416862578831</v>
+        <v>6.132587143920698</v>
       </c>
       <c r="P7" t="n">
-        <v>346.8283997560552</v>
+        <v>346.8124796310365</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36987,28 +37317,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2266809933166963</v>
+        <v>0.2314341284735988</v>
       </c>
       <c r="J8" t="n">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="K8" t="n">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="L8" t="n">
-        <v>0.07582558007548867</v>
+        <v>0.0801307709830511</v>
       </c>
       <c r="M8" t="n">
-        <v>4.543662289249866</v>
+        <v>4.521539349231211</v>
       </c>
       <c r="N8" t="n">
-        <v>32.44695798345766</v>
+        <v>32.20657199979716</v>
       </c>
       <c r="O8" t="n">
-        <v>5.696223133222369</v>
+        <v>5.67508343549213</v>
       </c>
       <c r="P8" t="n">
-        <v>346.5556424428233</v>
+        <v>346.5017782295489</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37065,28 +37395,28 @@
         <v>0.1602</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2981153121021834</v>
+        <v>0.3135979067542859</v>
       </c>
       <c r="J9" t="n">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="K9" t="n">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09317868225323189</v>
+        <v>0.1026797208425576</v>
       </c>
       <c r="M9" t="n">
-        <v>5.288434447326797</v>
+        <v>5.309361559711473</v>
       </c>
       <c r="N9" t="n">
-        <v>44.81044878226</v>
+        <v>45.0165325996561</v>
       </c>
       <c r="O9" t="n">
-        <v>6.694060709484192</v>
+        <v>6.709436086561679</v>
       </c>
       <c r="P9" t="n">
-        <v>350.5203796007339</v>
+        <v>350.3449490295267</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37143,28 +37473,28 @@
         <v>0.1037</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3244237899826748</v>
+        <v>0.3383506542847005</v>
       </c>
       <c r="J10" t="n">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="K10" t="n">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="L10" t="n">
-        <v>0.09465227032944534</v>
+        <v>0.1030759965907994</v>
       </c>
       <c r="M10" t="n">
-        <v>5.841535764062873</v>
+        <v>5.849030694660834</v>
       </c>
       <c r="N10" t="n">
-        <v>52.15732848249893</v>
+        <v>52.17891835738551</v>
       </c>
       <c r="O10" t="n">
-        <v>7.22200307965172</v>
+        <v>7.223497654002908</v>
       </c>
       <c r="P10" t="n">
-        <v>356.6368535413654</v>
+        <v>356.4790448055255</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37221,28 +37551,28 @@
         <v>0.0381</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1165451606453879</v>
+        <v>0.1176332847264838</v>
       </c>
       <c r="J11" t="n">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="K11" t="n">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01594013820355766</v>
+        <v>0.01655702579862417</v>
       </c>
       <c r="M11" t="n">
-        <v>5.273518147470055</v>
+        <v>5.233223585792577</v>
       </c>
       <c r="N11" t="n">
-        <v>43.44336882254548</v>
+        <v>43.05169269033409</v>
       </c>
       <c r="O11" t="n">
-        <v>6.591158382450347</v>
+        <v>6.561378871116505</v>
       </c>
       <c r="P11" t="n">
-        <v>360.1038613633883</v>
+        <v>360.0915155238674</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -37303,28 +37633,28 @@
         <v>0.0272</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4815722832519614</v>
+        <v>-0.4628427506511507</v>
       </c>
       <c r="J12" t="n">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="K12" t="n">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1485453970296574</v>
+        <v>0.139628151323689</v>
       </c>
       <c r="M12" t="n">
-        <v>6.66463429513854</v>
+        <v>6.704158028685478</v>
       </c>
       <c r="N12" t="n">
-        <v>68.87011932174694</v>
+        <v>69.14217903033675</v>
       </c>
       <c r="O12" t="n">
-        <v>8.298802282362615</v>
+        <v>8.315177630714617</v>
       </c>
       <c r="P12" t="n">
-        <v>365.2618764430216</v>
+        <v>365.0496398634435</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -37366,7 +37696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M646"/>
+  <dimension ref="A1:M652"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80651,6 +80981,408 @@
         </is>
       </c>
     </row>
+    <row r="647">
+      <c r="A647" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:13:56+00:00</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>-45.56273654635072,170.73166612708735</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>-45.563317434821464,170.7312829271002</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>-45.563863092831625,170.73084128445734</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>-45.56440929277132,170.73041875115257</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>-45.56497130721121,170.73002107029217</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>-45.56552139171726,170.72958800578266</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>-45.56612223576419,170.72930911267343</t>
+        </is>
+      </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>-45.56674265386951,170.72910244705332</t>
+        </is>
+      </c>
+      <c r="J647" t="inlineStr">
+        <is>
+          <t>-45.567331407748426,170.72883272958018</t>
+        </is>
+      </c>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>-45.56789661146319,170.72844875496816</t>
+        </is>
+      </c>
+      <c r="L647" t="inlineStr">
+        <is>
+          <t>-45.5684744727827,170.72811730357674</t>
+        </is>
+      </c>
+      <c r="M647" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:19:55+00:00</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>-45.56273659842484,170.73166623154475</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>-45.563313841692036,170.73127571948322</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>-45.56385413954667,170.73082115549892</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>-45.564408439302845,170.73041649573986</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>-45.56496974186343,170.7300167427862</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>-45.565522712187146,170.72959179193094</t>
+        </is>
+      </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>-45.566124613370995,170.7293164386033</t>
+        </is>
+      </c>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>-45.56674688091815,170.72911617332278</t>
+        </is>
+      </c>
+      <c r="J648" t="inlineStr">
+        <is>
+          <t>-45.56733587694674,170.7288493598368</t>
+        </is>
+      </c>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>-45.56790007610859,170.7284622277355</t>
+        </is>
+      </c>
+      <c r="L648" t="inlineStr">
+        <is>
+          <t>-45.56848170816929,170.7281431227341</t>
+        </is>
+      </c>
+      <c r="M648" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>-45.562736233905966,170.73166550034304</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>-45.56331644540906,170.73128094239402</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>-45.56385423581857,170.7308213719393</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>-45.5644107009942,170.73042247258365</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>-45.56497134840456,170.73002118417392</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>-45.56552655355336,170.72960280618142</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>-45.566124613370995,170.7293164386033</t>
+        </is>
+      </c>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>-45.5667458331883,170.72911277108486</t>
+        </is>
+      </c>
+      <c r="J649" t="inlineStr">
+        <is>
+          <t>-45.56733722735152,170.72885438480697</t>
+        </is>
+      </c>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>-45.567903447949504,170.7284753396268</t>
+        </is>
+      </c>
+      <c r="L649" t="inlineStr">
+        <is>
+          <t>-45.5684838421071,170.72815073760214</t>
+        </is>
+      </c>
+      <c r="M649" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:15+00:00</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>-45.562731599308435,170.73165620363662</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>-45.56331582051699,170.73127968889537</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>-45.563854572770225,170.73082212948066</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>-45.564408268609164,170.73041604465735</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>-45.56497241943189,170.73002414509918</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>-45.565525953339964,170.72960108520468</t>
+        </is>
+      </c>
+      <c r="H650" t="inlineStr">
+        <is>
+          <t>-45.5661251039882,170.72931795030317</t>
+        </is>
+      </c>
+      <c r="I650" t="inlineStr">
+        <is>
+          <t>-45.566742545483635,170.72910209509772</t>
+        </is>
+      </c>
+      <c r="J650" t="inlineStr">
+        <is>
+          <t>-45.56733491237177,170.72884577057258</t>
+        </is>
+      </c>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>-45.56790193216799,170.72846944529016</t>
+        </is>
+      </c>
+      <c r="L650" t="inlineStr">
+        <is>
+          <t>-45.56848000768724,170.72813705463662</t>
+        </is>
+      </c>
+      <c r="M650" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:14:16+00:00</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>-45.562728526934364,170.7316500406523</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>-45.563313737543346,170.7312755105668</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>-45.56385389886693,170.730820614398</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>-45.56440647632521,170.73041130829094</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>-45.56497093647096,170.73002004535653</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>-45.565525353126525,170.72959936422797</t>
+        </is>
+      </c>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>-45.5661236321365,170.72931341520356</t>
+        </is>
+      </c>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>-45.56674063066616,170.7290958772157</t>
+        </is>
+      </c>
+      <c r="J651" t="inlineStr">
+        <is>
+          <t>-45.5673311183758,170.7288316528011</t>
+        </is>
+      </c>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>-45.56790261272299,170.72847209172699</t>
+        </is>
+      </c>
+      <c r="L651" t="inlineStr">
+        <is>
+          <t>-45.56847860729002,170.72813205738012</t>
+        </is>
+      </c>
+      <c r="M651" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:32+00:00</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>-45.562728526934364,170.7316500406523</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>-45.56331618503736,170.7312804201029</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>-45.56385620939243,170.73082580896724</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>-45.564407287120346,170.73041345093284</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>-45.56497250181861,170.73002437286266</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>-45.56552743386631,170.72960533028072</t>
+        </is>
+      </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>-45.566125519125826,170.72931922943386</t>
+        </is>
+      </c>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>-45.5667406667948,170.72909599453422</t>
+        </is>
+      </c>
+      <c r="J652" t="inlineStr">
+        <is>
+          <t>-45.567332436628824,170.72883655812822</t>
+        </is>
+      </c>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>-45.567903695424,170.72847630196753</t>
+        </is>
+      </c>
+      <c r="L652" t="inlineStr">
+        <is>
+          <t>-45.56847867397561,170.72813229534472</t>
+        </is>
+      </c>
+      <c r="M652" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0494/nzd0494.xlsx
+++ b/data/nzd0494/nzd0494.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M652"/>
+  <dimension ref="A1:M656"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29788,6 +29788,186 @@
         <v>362.08</v>
       </c>
       <c r="M652" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:14:11+00:00</t>
+        </is>
+      </c>
+      <c r="B653" t="n">
+        <v>330.57</v>
+      </c>
+      <c r="C653" t="n">
+        <v>344.12</v>
+      </c>
+      <c r="D653" t="n">
+        <v>349.09</v>
+      </c>
+      <c r="E653" t="n">
+        <v>349.69</v>
+      </c>
+      <c r="F653" t="n">
+        <v>350.44</v>
+      </c>
+      <c r="G653" t="n">
+        <v>348.45</v>
+      </c>
+      <c r="H653" t="n">
+        <v>355.61</v>
+      </c>
+      <c r="I653" t="n">
+        <v>365.75</v>
+      </c>
+      <c r="J653" t="n">
+        <v>372.1</v>
+      </c>
+      <c r="K653" t="n">
+        <v>364.12</v>
+      </c>
+      <c r="L653" t="n">
+        <v>361.22</v>
+      </c>
+      <c r="M653" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B654" t="n">
+        <v>329.78</v>
+      </c>
+      <c r="C654" t="n">
+        <v>343.85</v>
+      </c>
+      <c r="D654" t="n">
+        <v>349.31</v>
+      </c>
+      <c r="E654" t="n">
+        <v>349.51</v>
+      </c>
+      <c r="F654" t="n">
+        <v>349.97</v>
+      </c>
+      <c r="G654" t="n">
+        <v>348.16</v>
+      </c>
+      <c r="H654" t="n">
+        <v>355.59</v>
+      </c>
+      <c r="I654" t="n">
+        <v>365.35</v>
+      </c>
+      <c r="J654" t="n">
+        <v>371.71</v>
+      </c>
+      <c r="K654" t="n">
+        <v>364.26</v>
+      </c>
+      <c r="L654" t="n">
+        <v>361.37</v>
+      </c>
+      <c r="M654" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:08+00:00</t>
+        </is>
+      </c>
+      <c r="B655" t="n">
+        <v>329.96</v>
+      </c>
+      <c r="C655" t="n">
+        <v>343.9</v>
+      </c>
+      <c r="D655" t="n">
+        <v>349.48</v>
+      </c>
+      <c r="E655" t="n">
+        <v>349.42</v>
+      </c>
+      <c r="F655" t="n">
+        <v>349.84</v>
+      </c>
+      <c r="G655" t="n">
+        <v>348.37</v>
+      </c>
+      <c r="H655" t="n">
+        <v>355.66</v>
+      </c>
+      <c r="I655" t="n">
+        <v>365.31</v>
+      </c>
+      <c r="J655" t="n">
+        <v>371.28</v>
+      </c>
+      <c r="K655" t="n">
+        <v>364.9</v>
+      </c>
+      <c r="L655" t="n">
+        <v>362.45</v>
+      </c>
+      <c r="M655" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B656" t="n">
+        <v>329.75</v>
+      </c>
+      <c r="C656" t="n">
+        <v>343.94</v>
+      </c>
+      <c r="D656" t="n">
+        <v>349.41</v>
+      </c>
+      <c r="E656" t="n">
+        <v>349.09</v>
+      </c>
+      <c r="F656" t="n">
+        <v>349.49</v>
+      </c>
+      <c r="G656" t="n">
+        <v>348.01</v>
+      </c>
+      <c r="H656" t="n">
+        <v>355.41</v>
+      </c>
+      <c r="I656" t="n">
+        <v>365.15</v>
+      </c>
+      <c r="J656" t="n">
+        <v>370.68</v>
+      </c>
+      <c r="K656" t="n">
+        <v>365.42</v>
+      </c>
+      <c r="L656" t="n">
+        <v>363.29</v>
+      </c>
+      <c r="M656" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29804,7 +29984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B687"/>
+  <dimension ref="A1:B691"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36677,6 +36857,46 @@
       </c>
       <c r="B687" t="n">
         <v>-0.06</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B688" t="n">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B689" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B690" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B691" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -36845,28 +37065,28 @@
         <v>0.122</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2508906731333573</v>
+        <v>-0.2518402134956034</v>
       </c>
       <c r="J2" t="n">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="K2" t="n">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08439075145266406</v>
+        <v>0.08600191216661224</v>
       </c>
       <c r="M2" t="n">
-        <v>4.723802986192278</v>
+        <v>4.699014207097299</v>
       </c>
       <c r="N2" t="n">
-        <v>35.77233398198674</v>
+        <v>35.55809007722453</v>
       </c>
       <c r="O2" t="n">
-        <v>5.980997741346066</v>
+        <v>5.963060462315013</v>
       </c>
       <c r="P2" t="n">
-        <v>337.5512854333911</v>
+        <v>337.5620816080819</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -36927,28 +37147,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2434874674974391</v>
+        <v>-0.2414215982172404</v>
       </c>
       <c r="J3" t="n">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="K3" t="n">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1275275728456753</v>
+        <v>0.1270157574531783</v>
       </c>
       <c r="M3" t="n">
-        <v>3.717543746480941</v>
+        <v>3.704714792686933</v>
       </c>
       <c r="N3" t="n">
-        <v>21.24534405301581</v>
+        <v>21.13256103196959</v>
       </c>
       <c r="O3" t="n">
-        <v>4.609267192625722</v>
+        <v>4.597016535968692</v>
       </c>
       <c r="P3" t="n">
-        <v>348.8373493137251</v>
+        <v>348.8138692252435</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37005,28 +37225,28 @@
         <v>0.1492</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.199468572137625</v>
+        <v>-0.1973464089676333</v>
       </c>
       <c r="J4" t="n">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="K4" t="n">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08439466357780656</v>
+        <v>0.08370526782619847</v>
       </c>
       <c r="M4" t="n">
-        <v>3.714566675924674</v>
+        <v>3.701588014861873</v>
       </c>
       <c r="N4" t="n">
-        <v>22.61024213449626</v>
+        <v>22.49012887596573</v>
       </c>
       <c r="O4" t="n">
-        <v>4.755022832174022</v>
+        <v>4.742375868271697</v>
       </c>
       <c r="P4" t="n">
-        <v>352.9721151298219</v>
+        <v>352.9479920993189</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37083,28 +37303,28 @@
         <v>0.1198</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.162759351123446</v>
+        <v>-0.1598482703634238</v>
       </c>
       <c r="J5" t="n">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="K5" t="n">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06205456632083406</v>
+        <v>0.06064484917140944</v>
       </c>
       <c r="M5" t="n">
-        <v>3.626256418547872</v>
+        <v>3.61716720787474</v>
       </c>
       <c r="N5" t="n">
-        <v>20.97290814445818</v>
+        <v>20.87867201320218</v>
       </c>
       <c r="O5" t="n">
-        <v>4.579618777197309</v>
+        <v>4.569318550200038</v>
       </c>
       <c r="P5" t="n">
-        <v>351.4463620158937</v>
+        <v>351.413277263668</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37161,28 +37381,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.06150718367852276</v>
+        <v>-0.05744140818292157</v>
       </c>
       <c r="J6" t="n">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="K6" t="n">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007057587062186843</v>
+        <v>0.006227734519823391</v>
       </c>
       <c r="M6" t="n">
-        <v>4.048803100759519</v>
+        <v>4.043717129114627</v>
       </c>
       <c r="N6" t="n">
-        <v>27.87933610494569</v>
+        <v>27.77525315270437</v>
       </c>
       <c r="O6" t="n">
-        <v>5.280088645557543</v>
+        <v>5.270223254540966</v>
       </c>
       <c r="P6" t="n">
-        <v>348.2868192795383</v>
+        <v>348.2406121548105</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37239,28 +37459,28 @@
         <v>0.1734</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0004925276428860764</v>
+        <v>0.001288436250311091</v>
       </c>
       <c r="J7" t="n">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="K7" t="n">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="L7" t="n">
-        <v>3.378598177894432e-07</v>
+        <v>2.342074347905232e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>4.795404112844887</v>
+        <v>4.774594771916344</v>
       </c>
       <c r="N7" t="n">
-        <v>37.60862507778143</v>
+        <v>37.39170462060873</v>
       </c>
       <c r="O7" t="n">
-        <v>6.132587143920698</v>
+        <v>6.11487568316877</v>
       </c>
       <c r="P7" t="n">
-        <v>346.8124796310365</v>
+        <v>346.7922384494214</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37317,28 +37537,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2314341284735988</v>
+        <v>0.2349144946264047</v>
       </c>
       <c r="J8" t="n">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="K8" t="n">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0801307709830511</v>
+        <v>0.08325038955191599</v>
       </c>
       <c r="M8" t="n">
-        <v>4.521539349231211</v>
+        <v>4.508574649251266</v>
       </c>
       <c r="N8" t="n">
-        <v>32.20657199979716</v>
+        <v>32.05790788981455</v>
       </c>
       <c r="O8" t="n">
-        <v>5.67508343549213</v>
+        <v>5.661970318697772</v>
       </c>
       <c r="P8" t="n">
-        <v>346.5017782295489</v>
+        <v>346.4622207114779</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37395,28 +37615,28 @@
         <v>0.1602</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3135979067542859</v>
+        <v>0.3217073947362744</v>
       </c>
       <c r="J9" t="n">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="K9" t="n">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1026797208425576</v>
+        <v>0.1081951273906188</v>
       </c>
       <c r="M9" t="n">
-        <v>5.309361559711473</v>
+        <v>5.313531663433102</v>
       </c>
       <c r="N9" t="n">
-        <v>45.0165325996561</v>
+        <v>45.00236254058108</v>
       </c>
       <c r="O9" t="n">
-        <v>6.709436086561679</v>
+        <v>6.708380023566128</v>
       </c>
       <c r="P9" t="n">
-        <v>350.3449490295267</v>
+        <v>350.2527790223401</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37473,28 +37693,28 @@
         <v>0.1037</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3383506542847005</v>
+        <v>0.3455369240214191</v>
       </c>
       <c r="J10" t="n">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="K10" t="n">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1030759965907994</v>
+        <v>0.1079161599521008</v>
       </c>
       <c r="M10" t="n">
-        <v>5.849030694660834</v>
+        <v>5.845207959703124</v>
       </c>
       <c r="N10" t="n">
-        <v>52.17891835738551</v>
+        <v>52.0665981289205</v>
       </c>
       <c r="O10" t="n">
-        <v>7.223497654002908</v>
+        <v>7.215718822745278</v>
       </c>
       <c r="P10" t="n">
-        <v>356.4790448055255</v>
+        <v>356.3973729165157</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37551,28 +37771,28 @@
         <v>0.0381</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1176332847264838</v>
+        <v>0.1193737413046336</v>
       </c>
       <c r="J11" t="n">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="K11" t="n">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01655702579862417</v>
+        <v>0.0172599384525256</v>
       </c>
       <c r="M11" t="n">
-        <v>5.233223585792577</v>
+        <v>5.209774365439084</v>
       </c>
       <c r="N11" t="n">
-        <v>43.05169269033409</v>
+        <v>42.80239956145989</v>
       </c>
       <c r="O11" t="n">
-        <v>6.561378871116505</v>
+        <v>6.542354282783827</v>
       </c>
       <c r="P11" t="n">
-        <v>360.0915155238674</v>
+        <v>360.0717255805663</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -37633,28 +37853,28 @@
         <v>0.0272</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4628427506511507</v>
+        <v>-0.4511424528650635</v>
       </c>
       <c r="J12" t="n">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="K12" t="n">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="L12" t="n">
-        <v>0.139628151323689</v>
+        <v>0.1342059367783026</v>
       </c>
       <c r="M12" t="n">
-        <v>6.704158028685478</v>
+        <v>6.727239801417663</v>
       </c>
       <c r="N12" t="n">
-        <v>69.14217903033675</v>
+        <v>69.26619911594089</v>
       </c>
       <c r="O12" t="n">
-        <v>8.315177630714617</v>
+        <v>8.322631742179928</v>
       </c>
       <c r="P12" t="n">
-        <v>365.0496398634435</v>
+        <v>364.9166402917346</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -37696,7 +37916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M652"/>
+  <dimension ref="A1:M656"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81383,6 +81603,274 @@
         </is>
       </c>
     </row>
+    <row r="653">
+      <c r="A653" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:14:11+00:00</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>-45.56272394440977,170.73164084840576</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>-45.56331415413809,170.7312763462325</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>-45.56385625752837,170.73082591718745</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>-45.56440711642664,170.73041299985033</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>-45.56497299613889,170.73002573944362</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>-45.56552859427874,170.72960865750264</t>
+        </is>
+      </c>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>-45.56612585878388,170.72932027599538</t>
+        </is>
+      </c>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>-45.56673933003527,170.7290916537489</t>
+        </is>
+      </c>
+      <c r="J653" t="inlineStr">
+        <is>
+          <t>-45.56733153635848,170.7288332081487</t>
+        </is>
+      </c>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>-45.56790233431413,170.72847100909374</t>
+        </is>
+      </c>
+      <c r="L653" t="inlineStr">
+        <is>
+          <t>-45.568475806494945,170.7281220628679</t>
+        </is>
+      </c>
+      <c r="M653" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>-45.56271983055183,170.73163259627665</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>-45.56331274813082,170.73127352586087</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>-45.56385731651915,170.7308282980318</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>-45.564406348304914,170.73041096997906</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>-45.56497106005104,170.73002038700176</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>-45.56552743386631,170.72960533028072</t>
+        </is>
+      </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>-45.56612578330432,170.72932004342616</t>
+        </is>
+      </c>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>-45.56673788488962,170.72908696100828</t>
+        </is>
+      </c>
+      <c r="J654" t="inlineStr">
+        <is>
+          <t>-45.567330282410346,170.72882854210593</t>
+        </is>
+      </c>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>-45.56790276739457,170.7284726931899</t>
+        </is>
+      </c>
+      <c r="L654" t="inlineStr">
+        <is>
+          <t>-45.56847630663699,170.72812384760218</t>
+        </is>
+      </c>
+      <c r="M654" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:08+00:00</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>-45.562720767886596,170.7316344765085</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>-45.56331300850254,170.73127404815187</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>-45.56385813483017,170.73083013777529</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>-45.56440596424405,170.73040995504346</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>-45.564970524537344,170.73001890653916</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>-45.56552827416498,170.7296077396483</t>
+        </is>
+      </c>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>-45.5661260474828,170.72932085741843</t>
+        </is>
+      </c>
+      <c r="I655" t="inlineStr">
+        <is>
+          <t>-45.56673774037503,170.72908649173422</t>
+        </is>
+      </c>
+      <c r="J655" t="inlineStr">
+        <is>
+          <t>-45.567328899851915,170.72882339749495</t>
+        </is>
+      </c>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>-45.56790474719056,170.72848039191564</t>
+        </is>
+      </c>
+      <c r="L655" t="inlineStr">
+        <is>
+          <t>-45.568479907658876,170.7281366976897</t>
+        </is>
+      </c>
+      <c r="M655" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>-45.562719674329365,170.73163228290468</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>-45.56331321679992,170.7312744659847</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>-45.563857797878576,170.73082938023384</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>-45.56440455602077,170.730406233613</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>-45.56496908276959,170.7300149206785</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>-45.565526833652946,170.72960360930392</t>
+        </is>
+      </c>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>-45.5661251039882,170.72931795030317</t>
+        </is>
+      </c>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>-45.566737162316734,170.72908461463805</t>
+        </is>
+      </c>
+      <c r="J656" t="inlineStr">
+        <is>
+          <t>-45.56732697070026,170.7288162189684</t>
+        </is>
+      </c>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>-45.56790635577441,170.72848664713072</t>
+        </is>
+      </c>
+      <c r="L656" t="inlineStr">
+        <is>
+          <t>-45.568482708452706,170.72814669220344</t>
+        </is>
+      </c>
+      <c r="M656" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0494/nzd0494.xlsx
+++ b/data/nzd0494/nzd0494.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M656"/>
+  <dimension ref="A1:M658"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29968,6 +29968,96 @@
         <v>363.29</v>
       </c>
       <c r="M656" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:14:25+00:00</t>
+        </is>
+      </c>
+      <c r="B657" t="n">
+        <v>329.82</v>
+      </c>
+      <c r="C657" t="n">
+        <v>344.23</v>
+      </c>
+      <c r="D657" t="n">
+        <v>349.61</v>
+      </c>
+      <c r="E657" t="n">
+        <v>349.19</v>
+      </c>
+      <c r="F657" t="n">
+        <v>349.77</v>
+      </c>
+      <c r="G657" t="n">
+        <v>348.14</v>
+      </c>
+      <c r="H657" t="n">
+        <v>355.44</v>
+      </c>
+      <c r="I657" t="n">
+        <v>365.18</v>
+      </c>
+      <c r="J657" t="n">
+        <v>370.33</v>
+      </c>
+      <c r="K657" t="n">
+        <v>364.52</v>
+      </c>
+      <c r="L657" t="n">
+        <v>362.2</v>
+      </c>
+      <c r="M657" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B658" t="n">
+        <v>330.73</v>
+      </c>
+      <c r="C658" t="n">
+        <v>344.77</v>
+      </c>
+      <c r="D658" t="n">
+        <v>350.15</v>
+      </c>
+      <c r="E658" t="n">
+        <v>349.57</v>
+      </c>
+      <c r="F658" t="n">
+        <v>349.52</v>
+      </c>
+      <c r="G658" t="n">
+        <v>348.72</v>
+      </c>
+      <c r="H658" t="n">
+        <v>354.83</v>
+      </c>
+      <c r="I658" t="n">
+        <v>365.4</v>
+      </c>
+      <c r="J658" t="n">
+        <v>370.51</v>
+      </c>
+      <c r="K658" t="n">
+        <v>365.98</v>
+      </c>
+      <c r="L658" t="n">
+        <v>365.32</v>
+      </c>
+      <c r="M658" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29984,7 +30074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B691"/>
+  <dimension ref="A1:B693"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36897,6 +36987,26 @@
       </c>
       <c r="B691" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B692" t="n">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B693" t="n">
+        <v>0.43</v>
       </c>
     </row>
   </sheetData>
@@ -37065,28 +37175,28 @@
         <v>0.122</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2518402134956034</v>
+        <v>-0.2521326665277903</v>
       </c>
       <c r="J2" t="n">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="K2" t="n">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08600191216661224</v>
+        <v>0.08670235826606842</v>
       </c>
       <c r="M2" t="n">
-        <v>4.699014207097299</v>
+        <v>4.685950490573219</v>
       </c>
       <c r="N2" t="n">
-        <v>35.55809007722453</v>
+        <v>35.45118216741862</v>
       </c>
       <c r="O2" t="n">
-        <v>5.963060462315013</v>
+        <v>5.95408953303682</v>
       </c>
       <c r="P2" t="n">
-        <v>337.5620816080819</v>
+        <v>337.5654125704154</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -37147,28 +37257,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2414215982172404</v>
+        <v>-0.2400608560923733</v>
       </c>
       <c r="J3" t="n">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="K3" t="n">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1270157574531783</v>
+        <v>0.1264156045887203</v>
       </c>
       <c r="M3" t="n">
-        <v>3.704714792686933</v>
+        <v>3.699868080012554</v>
       </c>
       <c r="N3" t="n">
-        <v>21.13256103196959</v>
+        <v>21.08326875528862</v>
       </c>
       <c r="O3" t="n">
-        <v>4.597016535968692</v>
+        <v>4.591652072543021</v>
       </c>
       <c r="P3" t="n">
-        <v>348.8138692252435</v>
+        <v>348.7983480330518</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37225,28 +37335,28 @@
         <v>0.1492</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1973464089676333</v>
+        <v>-0.1959561118638671</v>
       </c>
       <c r="J4" t="n">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="K4" t="n">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08370526782619847</v>
+        <v>0.08307509168347427</v>
       </c>
       <c r="M4" t="n">
-        <v>3.701588014861873</v>
+        <v>3.69663031390804</v>
       </c>
       <c r="N4" t="n">
-        <v>22.49012887596573</v>
+        <v>22.43735352139455</v>
       </c>
       <c r="O4" t="n">
-        <v>4.742375868271697</v>
+        <v>4.736808368658643</v>
       </c>
       <c r="P4" t="n">
-        <v>352.9479920993189</v>
+        <v>352.9321338515408</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37303,28 +37413,28 @@
         <v>0.1198</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1598482703634238</v>
+        <v>-0.1584421665964947</v>
       </c>
       <c r="J5" t="n">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="K5" t="n">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06064484917140944</v>
+        <v>0.05997378872075632</v>
       </c>
       <c r="M5" t="n">
-        <v>3.61716720787474</v>
+        <v>3.612439691648991</v>
       </c>
       <c r="N5" t="n">
-        <v>20.87867201320218</v>
+        <v>20.83104634588564</v>
       </c>
       <c r="O5" t="n">
-        <v>4.569318550200038</v>
+        <v>4.564104112077818</v>
       </c>
       <c r="P5" t="n">
-        <v>351.413277263668</v>
+        <v>351.3972394773971</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37381,28 +37491,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.05744140818292157</v>
+        <v>-0.05562646201068235</v>
       </c>
       <c r="J6" t="n">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="K6" t="n">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="L6" t="n">
-        <v>0.006227734519823391</v>
+        <v>0.005875525754619026</v>
       </c>
       <c r="M6" t="n">
-        <v>4.043717129114627</v>
+        <v>4.040106297291056</v>
       </c>
       <c r="N6" t="n">
-        <v>27.77525315270437</v>
+        <v>27.71711161568893</v>
       </c>
       <c r="O6" t="n">
-        <v>5.270223254540966</v>
+        <v>5.264704323671837</v>
       </c>
       <c r="P6" t="n">
-        <v>348.2406121548105</v>
+        <v>348.2199147446622</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37459,28 +37569,28 @@
         <v>0.1734</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001288436250311091</v>
+        <v>0.002274319837722214</v>
       </c>
       <c r="J7" t="n">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="K7" t="n">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="L7" t="n">
-        <v>2.342074347905232e-06</v>
+        <v>7.344230825268028e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>4.774594771916344</v>
+        <v>4.764698095277952</v>
       </c>
       <c r="N7" t="n">
-        <v>37.39170462060873</v>
+        <v>37.28590026237779</v>
       </c>
       <c r="O7" t="n">
-        <v>6.11487568316877</v>
+        <v>6.106218163673632</v>
       </c>
       <c r="P7" t="n">
-        <v>346.7922384494214</v>
+        <v>346.7809922327826</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37537,28 +37647,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2349144946264047</v>
+        <v>0.2363377356222914</v>
       </c>
       <c r="J8" t="n">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="K8" t="n">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08325038955191599</v>
+        <v>0.08464677622469685</v>
       </c>
       <c r="M8" t="n">
-        <v>4.508574649251266</v>
+        <v>4.500842427331606</v>
       </c>
       <c r="N8" t="n">
-        <v>32.05790788981455</v>
+        <v>31.97683642107914</v>
       </c>
       <c r="O8" t="n">
-        <v>5.661970318697772</v>
+        <v>5.654806488384827</v>
       </c>
       <c r="P8" t="n">
-        <v>346.4622207114779</v>
+        <v>346.4459922697333</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37615,28 +37725,28 @@
         <v>0.1602</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3217073947362744</v>
+        <v>0.3255985214583799</v>
       </c>
       <c r="J9" t="n">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="K9" t="n">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1081951273906188</v>
+        <v>0.1109209800634938</v>
       </c>
       <c r="M9" t="n">
-        <v>5.313531663433102</v>
+        <v>5.315008066579632</v>
       </c>
       <c r="N9" t="n">
-        <v>45.00236254058108</v>
+        <v>44.98653815094151</v>
       </c>
       <c r="O9" t="n">
-        <v>6.708380023566128</v>
+        <v>6.707200470460198</v>
       </c>
       <c r="P9" t="n">
-        <v>350.2527790223401</v>
+        <v>350.2084016621145</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37693,28 +37803,28 @@
         <v>0.1037</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3455369240214191</v>
+        <v>0.3484081743928844</v>
       </c>
       <c r="J10" t="n">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="K10" t="n">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1079161599521008</v>
+        <v>0.1100401947593856</v>
       </c>
       <c r="M10" t="n">
-        <v>5.845207959703124</v>
+        <v>5.840085775708807</v>
       </c>
       <c r="N10" t="n">
-        <v>52.0665981289205</v>
+        <v>51.97407585236023</v>
       </c>
       <c r="O10" t="n">
-        <v>7.215718822745278</v>
+        <v>7.209304810615253</v>
       </c>
       <c r="P10" t="n">
-        <v>356.3973729165157</v>
+        <v>356.3646269959905</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37771,28 +37881,28 @@
         <v>0.0381</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1193737413046336</v>
+        <v>0.1205744476440629</v>
       </c>
       <c r="J11" t="n">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="K11" t="n">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0172599384525256</v>
+        <v>0.01771181648482101</v>
       </c>
       <c r="M11" t="n">
-        <v>5.209774365439084</v>
+        <v>5.199754014622321</v>
       </c>
       <c r="N11" t="n">
-        <v>42.80239956145989</v>
+        <v>42.68521175552371</v>
       </c>
       <c r="O11" t="n">
-        <v>6.542354282783827</v>
+        <v>6.533392055856108</v>
       </c>
       <c r="P11" t="n">
-        <v>360.0717255805663</v>
+        <v>360.0580253246233</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -37853,28 +37963,28 @@
         <v>0.0272</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4511424528650635</v>
+        <v>-0.4443605920564745</v>
       </c>
       <c r="J12" t="n">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="K12" t="n">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1342059367783026</v>
+        <v>0.1308584279014082</v>
       </c>
       <c r="M12" t="n">
-        <v>6.727239801417663</v>
+        <v>6.743970313297472</v>
       </c>
       <c r="N12" t="n">
-        <v>69.26619911594089</v>
+        <v>69.43060672165484</v>
       </c>
       <c r="O12" t="n">
-        <v>8.322631742179928</v>
+        <v>8.3325030286016</v>
       </c>
       <c r="P12" t="n">
-        <v>364.9166402917346</v>
+        <v>364.839281728881</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -37916,7 +38026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M656"/>
+  <dimension ref="A1:M658"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81871,6 +81981,140 @@
         </is>
       </c>
     </row>
+    <row r="657">
+      <c r="A657" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:14:25+00:00</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>-45.56272003884845,170.73163301410594</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>-45.563314726955845,170.73127749527285</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>-45.563858760597405,170.73083154463794</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>-45.564404982755114,170.73040736131918</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>-45.56497023618381,170.73001810936702</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>-45.565527353837865,170.72960510081714</t>
+        </is>
+      </c>
+      <c r="H657" t="inlineStr">
+        <is>
+          <t>-45.56612521720755,170.729318299157</t>
+        </is>
+      </c>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>-45.566737270702674,170.72908496659358</t>
+        </is>
+      </c>
+      <c r="J657" t="inlineStr">
+        <is>
+          <t>-45.56732584536158,170.7288120314948</t>
+        </is>
+      </c>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>-45.567903571686756,170.72847582079717</t>
+        </is>
+      </c>
+      <c r="L657" t="inlineStr">
+        <is>
+          <t>-45.568479074089126,170.72813372313226</t>
+        </is>
+      </c>
+      <c r="M657" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>-45.5627247775961,170.7316425197232</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>-45.56331753897013,170.73128313601669</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>-45.56386135993804,170.7308373885294</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>-45.56440660434549,170.73041164660282</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>-45.564969206349694,170.7300152623237</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>-45.56552967466265,170.7296117552611</t>
+        </is>
+      </c>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>-45.56612291508048,170.72931120579617</t>
+        </is>
+      </c>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>-45.566738065532824,170.7290875476008</t>
+        </is>
+      </c>
+      <c r="J658" t="inlineStr">
+        <is>
+          <t>-45.56732642410721,170.72881418505264</t>
+        </is>
+      </c>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>-45.567908088095116,170.7284933835166</t>
+        </is>
+      </c>
+      <c r="L658" t="inlineStr">
+        <is>
+          <t>-45.56848947703424,170.72817084561578</t>
+        </is>
+      </c>
+      <c r="M658" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
